--- a/sw/src/MSPM0_Pins_AssignmentsLab6.xlsx
+++ b/sw/src/MSPM0_Pins_AssignmentsLab6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Dropbox\EE345L Class\EE445LTeachingMaterials\000000_COMMON_WEB_FILES\MSPM0LabSolutions\ECE445L_Lab6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utexas-my.sharepoint.com/personal/tsp824_eid_utexas_edu/Documents/Desktop/Tanai's Data/UT Undergrad ALL/UT Classes ALL/ECE 445L Labs/ece445l_lab6_fall26-tanai-prathapam/sw/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252CD834-2E5C-4AA7-AAB9-A10D4CBBB82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{252CD834-2E5C-4AA7-AAB9-A10D4CBBB82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D22AAED-DB93-44D2-AB1A-9D6789325BB1}"/>
   <bookViews>
-    <workbookView xWindow="29805" yWindow="1875" windowWidth="27480" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VSSOP-32" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="390">
   <si>
     <t>PA25</t>
   </si>
@@ -682,21 +682,9 @@
     <t>ST7735R Reset</t>
   </si>
   <si>
-    <t xml:space="preserve">ADC0_7 Slide pot </t>
-  </si>
-  <si>
-    <t>LED output</t>
-  </si>
-  <si>
     <t>Switch input</t>
   </si>
   <si>
-    <t>Buzzer</t>
-  </si>
-  <si>
-    <t>DACOUT</t>
-  </si>
-  <si>
     <t>10pF C0G 5%</t>
   </si>
   <si>
@@ -901,12 +889,6 @@
     <t>10k</t>
   </si>
   <si>
-    <t>R4 R6</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
     <t>SW1 SW2 SW3 SW4 SW5</t>
   </si>
   <si>
@@ -1018,21 +1000,12 @@
     <t>47KEBK-ND</t>
   </si>
   <si>
-    <t>20k</t>
-  </si>
-  <si>
     <t>CFR-12JB-10K</t>
   </si>
   <si>
     <t>10KEBK-ND</t>
   </si>
   <si>
-    <t>CFR-12JB-20K</t>
-  </si>
-  <si>
-    <t>20KEBK-ND</t>
-  </si>
-  <si>
     <t>CFR-12JB-100K</t>
   </si>
   <si>
@@ -1066,18 +1039,12 @@
     <t>PA0 and PA1 are open drain (only go low, not high)</t>
   </si>
   <si>
-    <t>CLK_OUT (optional)</t>
-  </si>
-  <si>
     <t>1.0uF Ceramic</t>
   </si>
   <si>
     <t>C3,C5</t>
   </si>
   <si>
-    <t>C6 C8</t>
-  </si>
-  <si>
     <t>FG18X5R1H105KRT00</t>
   </si>
   <si>
@@ -1127,13 +1094,128 @@
   </si>
   <si>
     <t>Total ($)</t>
+  </si>
+  <si>
+    <t>Unused</t>
+  </si>
+  <si>
+    <t>Logic-analyzer/debug connector J7, pin 1</t>
+  </si>
+  <si>
+    <t>Logic-analyzer/debug connector J7, pin 8</t>
+  </si>
+  <si>
+    <t>Logic-analyzer/debug connector J7, pin 2; 100 kΩ to GND</t>
+  </si>
+  <si>
+    <t>Logic-analyzer/debug connector J7, pin 3</t>
+  </si>
+  <si>
+    <t>AD8300 DAC chip select, SPI0_CS0</t>
+  </si>
+  <si>
+    <t>AD8300 DAC load control, active-low LD</t>
+  </si>
+  <si>
+    <t>AD8300 DAC clock, SPI0_SCK</t>
+  </si>
+  <si>
+    <t>Heartbeat LED D2 through R2</t>
+  </si>
+  <si>
+    <t>AD8300 DAC serial data, SPI0_PICO/MOSI</t>
+  </si>
+  <si>
+    <t>No external circuit connected</t>
+  </si>
+  <si>
+    <t>Potentiometer ADC input, ADC0_7; test point TP1</t>
+  </si>
+  <si>
+    <t>AD8300 DAC clear control, active-low CLR</t>
+  </si>
+  <si>
+    <t>C13 C15</t>
+  </si>
+  <si>
+    <t>1 uF nonpolar bypass capacitors</t>
+  </si>
+  <si>
+    <t>C6 C8 C12 C14</t>
+  </si>
+  <si>
+    <t>IC1</t>
+  </si>
+  <si>
+    <t>12-bit serial voltage-output DAC, internal reference, 0 to 2.0475 V</t>
+  </si>
+  <si>
+    <t>ECE445L:SOIC127P600X175-8N</t>
+  </si>
+  <si>
+    <t>Capacitor_THT:C_Rect_L4.0mm_W2.5mm_P2.50mm</t>
+  </si>
+  <si>
+    <t>Analog Devices</t>
+  </si>
+  <si>
+    <t>AD8300ARZ</t>
+  </si>
+  <si>
+    <t>584-AD8300ARZ</t>
+  </si>
+  <si>
+    <t>IC2</t>
+  </si>
+  <si>
+    <t>Quad precision RRIO CMOS op amp; unity-gain buffer; SOIC-14</t>
+  </si>
+  <si>
+    <t>Package_SO:SOIC-14_3.9x8.7mm_P1.27mm</t>
+  </si>
+  <si>
+    <t>AD8604WARZ</t>
+  </si>
+  <si>
+    <t>584-AD8604WARZ</t>
+  </si>
+  <si>
+    <t>R4 R6 R8 R9 R5</t>
+  </si>
+  <si>
+    <t>J6</t>
+  </si>
+  <si>
+    <t>2-pin power jumper/header, 2.54 mm pitch</t>
+  </si>
+  <si>
+    <t>ECE445L:PinHeader_1x02_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t>J7</t>
+  </si>
+  <si>
+    <t>2x06 logic-analyzer/debug header, 2.54 mm pitch</t>
+  </si>
+  <si>
+    <t>Connector_PinHeader_2.54mm:PinHeader_2x06_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t>H1 H2 H3 H4</t>
+  </si>
+  <si>
+    <t>4-40 mounting-hole PCB features</t>
+  </si>
+  <si>
+    <t>ECE445L:MountingHole_4_40</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
@@ -1292,7 +1374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1323,18 +1405,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1357,40 +1432,72 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5344,7 +5451,7 @@
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>419862</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>151738</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5391,10 +5498,10 @@
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>61545</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5785,18 +5892,18 @@
   <dimension ref="A1:XEU44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" style="23" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
     <col min="3" max="3" width="6.5703125" style="2" customWidth="1"/>
     <col min="4" max="4" width="5.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="6" style="2" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30.28515625" customWidth="1"/>
+    <col min="7" max="7" width="30.28515625" style="23" customWidth="1"/>
     <col min="8" max="8" width="5.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="23" t="s">
         <v>170</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -5805,32 +5912,32 @@
       <c r="E1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>216</v>
+      <c r="A2" s="24" t="s">
+        <v>214</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="16">
         <v>1</v>
       </c>
-      <c r="D2" s="22"/>
-      <c r="E2" s="20">
+      <c r="D2" s="19"/>
+      <c r="E2" s="17">
         <f t="shared" ref="E2:E15" si="0">E3+1</f>
         <v>32</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="30" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="25" t="s">
         <v>210</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -5843,15 +5950,15 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="30" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
+    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="26"/>
       <c r="B4" s="1" t="s">
         <v>171</v>
       </c>
@@ -5865,10 +5972,13 @@
       <c r="F4" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>217</v>
+      <c r="G4" s="23" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>352</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>37</v>
@@ -5880,15 +5990,17 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="28" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
+      <c r="G5" s="31" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>353</v>
+      </c>
       <c r="B6" s="1" t="s">
         <v>38</v>
       </c>
@@ -5902,9 +6014,12 @@
       <c r="F6" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="G6" s="23" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
+      <c r="A7" s="26"/>
       <c r="B7" s="1" t="s">
         <v>172</v>
       </c>
@@ -5918,12 +6033,12 @@
       <c r="F7" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="23" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -5937,12 +6052,12 @@
       <c r="F8" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="29" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="1" t="s">
         <v>174</v>
       </c>
@@ -5953,14 +6068,17 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="32" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
+        <v>355</v>
+      </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
@@ -5971,16 +6089,16 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="32" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>216</v>
+      <c r="A11" s="24" t="s">
+        <v>214</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>10</v>
@@ -5992,15 +6110,17 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="G11" s="26" t="s">
+      <c r="G11" s="32" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
+    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>356</v>
+      </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
@@ -6011,15 +6131,15 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="29" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="G12" s="33" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
         <v>176</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -6035,12 +6155,12 @@
       <c r="F13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>342</v>
+      <c r="G13" s="29" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="26" t="s">
         <v>175</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -6053,16 +6173,16 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="G14" s="32" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>216</v>
+      <c r="A15" s="24" t="s">
+        <v>214</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>14</v>
@@ -6074,18 +6194,20 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="27" t="s">
-        <v>215</v>
+      <c r="G15" s="34" t="s">
+        <v>360</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
+    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
+        <v>357</v>
+      </c>
       <c r="B16" s="1" t="s">
         <v>1</v>
       </c>
@@ -6099,41 +6221,46 @@
       <c r="F16" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="G16" s="23" t="s">
+        <v>359</v>
+      </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
+    <row r="17" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
+        <v>358</v>
+      </c>
       <c r="B17" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C17" s="5">
         <v>16</v>
       </c>
-      <c r="D17" s="21"/>
+      <c r="D17" s="18"/>
       <c r="E17" s="6">
         <v>17</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="12" t="s">
-        <v>216</v>
+      <c r="G17" s="35" t="s">
+        <v>214</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
     </row>
     <row r="18" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
+      <c r="A18" s="26"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
     </row>
     <row r="19" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>333</v>
+      <c r="A19" s="26" t="s">
+        <v>324</v>
       </c>
       <c r="B19" s="1">
         <f>32-6</f>
@@ -6149,16 +6276,16 @@
       <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>340</v>
+      <c r="A21" s="23" t="s">
+        <v>331</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>341</v>
+    <row r="22" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="23" t="s">
+        <v>332</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
@@ -12368,13 +12495,13 @@
       <c r="B38"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="15"/>
+      <c r="A39" s="27"/>
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="16"/>
+      <c r="A41" s="28"/>
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
@@ -12407,983 +12534,1087 @@
   <dimension ref="A1:O43"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" style="32" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" style="31" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" style="31" customWidth="1"/>
-    <col min="4" max="4" width="14" style="31" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="31" customWidth="1"/>
-    <col min="6" max="6" width="24" style="31" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="31" customWidth="1"/>
-    <col min="8" max="8" width="29.7109375" style="31" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="31" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="37"/>
-    <col min="11" max="16384" width="9.140625" style="31"/>
+    <col min="1" max="1" width="7.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" style="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.85546875" style="37" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" style="37" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="37" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.140625" style="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" style="37" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29" style="37" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" style="37" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" style="38" customWidth="1"/>
+    <col min="11" max="11" width="8.5703125" style="37" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6" style="37" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23" style="37" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.5703125" style="37" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.140625" style="37" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="37"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="I1" s="31" t="s">
-        <v>360</v>
-      </c>
-      <c r="K1" s="31" t="s">
-        <v>362</v>
+      <c r="I1" s="37" t="s">
+        <v>349</v>
+      </c>
+      <c r="K1" s="37" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="I2" s="31">
-        <f>SUM(I4:I51)</f>
-        <v>434.38</v>
-      </c>
-      <c r="K2" s="37">
-        <f>SUM(K4:K51)</f>
-        <v>54.120000000000005</v>
+      <c r="I2" s="37">
+        <f>SUM(I4:I50)</f>
+        <v>438.3</v>
+      </c>
+      <c r="K2" s="38">
+        <f>SUM(K4:K50)</f>
+        <v>80.84</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="37" t="s">
         <v>191</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="37" t="s">
         <v>192</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="H3" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="I3" s="31" t="s">
-        <v>359</v>
-      </c>
-      <c r="J3" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="K3" s="31" t="s">
-        <v>354</v>
+      <c r="I3" s="37" t="s">
+        <v>348</v>
+      </c>
+      <c r="J3" s="38" t="s">
+        <v>350</v>
+      </c>
+      <c r="K3" s="37" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="32">
+      <c r="A4" s="36">
         <v>2</v>
       </c>
-      <c r="B4" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>259</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>260</v>
-      </c>
-      <c r="G4" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="H4" s="30" t="s">
-        <v>273</v>
-      </c>
-      <c r="J4" s="37">
+      <c r="B4" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="G4" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="H4" s="39" t="s">
+        <v>269</v>
+      </c>
+      <c r="J4" s="38">
         <v>0.74</v>
       </c>
-      <c r="K4" s="37">
+      <c r="K4" s="38">
         <f>J4*A4</f>
         <v>1.48</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="32">
+      <c r="A5" s="36">
         <v>2</v>
       </c>
-      <c r="B5" s="31" t="s">
-        <v>344</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>343</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="E5" s="31" t="s">
-        <v>347</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>346</v>
-      </c>
-      <c r="G5" s="31" t="s">
+      <c r="B5" s="37" t="s">
+        <v>334</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>333</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F5" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="G5" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="H5" s="30" t="s">
-        <v>348</v>
-      </c>
-      <c r="J5" s="37">
+      <c r="H5" s="39" t="s">
+        <v>337</v>
+      </c>
+      <c r="J5" s="38">
         <v>0.11</v>
       </c>
-      <c r="K5" s="37">
+      <c r="K5" s="38">
         <f t="shared" ref="K5:K11" si="0">J5*A5</f>
         <v>0.22</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="32">
+      <c r="A6" s="36">
         <v>1</v>
       </c>
-      <c r="B6" s="31" t="s">
-        <v>264</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>265</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="H6" s="30" t="s">
-        <v>271</v>
-      </c>
-      <c r="J6" s="37">
+      <c r="B6" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="G6" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="H6" s="39" t="s">
+        <v>267</v>
+      </c>
+      <c r="J6" s="38">
         <v>0.3</v>
       </c>
-      <c r="K6" s="37">
+      <c r="K6" s="38">
         <f t="shared" si="0"/>
         <v>0.3</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="32">
+      <c r="A7" s="36">
         <v>2</v>
       </c>
-      <c r="B7" s="31" t="s">
-        <v>345</v>
-      </c>
-      <c r="C7" s="31" t="s">
+      <c r="B7" s="37" t="s">
+        <v>367</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="G7" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="H7" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="G7" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="H7" s="30" t="s">
-        <v>272</v>
-      </c>
-      <c r="J7" s="37">
+      <c r="J7" s="38">
         <v>0.36</v>
       </c>
-      <c r="K7" s="37">
+      <c r="K7" s="38">
         <f t="shared" si="0"/>
         <v>0.72</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="32">
+      <c r="A8" s="36">
         <v>1</v>
       </c>
-      <c r="B8" s="31" t="s">
-        <v>269</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>275</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="E8" s="31" t="s">
+      <c r="B8" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="E8" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="F8" s="31" t="s">
-        <v>261</v>
-      </c>
-      <c r="G8" s="31" t="s">
+      <c r="F8" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="G8" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="H8" s="31" t="s">
-        <v>262</v>
-      </c>
-      <c r="J8" s="37">
+      <c r="H8" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="J8" s="38">
         <v>0.21</v>
       </c>
-      <c r="K8" s="37">
+      <c r="K8" s="38">
         <f t="shared" si="0"/>
         <v>0.21</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="32">
+      <c r="A9" s="36">
         <v>1</v>
       </c>
-      <c r="B9" s="31" t="s">
-        <v>266</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="D9" s="31" t="s">
+      <c r="B9" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="C9" s="37" t="s">
         <v>263</v>
       </c>
-      <c r="G9" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="H9" s="31" t="s">
-        <v>274</v>
-      </c>
-      <c r="J9" s="37">
+      <c r="D9" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="G9" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="H9" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="J9" s="38">
         <v>0.46</v>
       </c>
-      <c r="K9" s="37">
+      <c r="K9" s="38">
         <f t="shared" si="0"/>
         <v>0.46</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+      <c r="A10" s="36">
         <v>2</v>
       </c>
-      <c r="B10" s="31" t="s">
-        <v>270</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="G10" s="31" t="s">
+      <c r="B10" s="37" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="G10" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="H10" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="J10" s="37">
+      <c r="H10" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="J10" s="38">
         <v>0.22</v>
       </c>
-      <c r="K10" s="37">
+      <c r="K10" s="38">
         <f t="shared" si="0"/>
         <v>0.44</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="32">
+      <c r="A11" s="36">
         <v>0</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="D11" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="E11" s="31" t="s">
+      <c r="D11" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="E11" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="F11" s="31" t="s">
+      <c r="F11" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="H11" s="31" t="s">
+      <c r="H11" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="J11" s="37">
+      <c r="J11" s="38">
         <v>0.22</v>
       </c>
-      <c r="K11" s="37">
+      <c r="K11" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
+    <row r="12" spans="1:15" ht="63" x14ac:dyDescent="0.25">
+      <c r="A12" s="36">
+        <v>2</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>365</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>366</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>371</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="J12" s="40">
+        <v>0.11</v>
+      </c>
+      <c r="K12" s="40">
+        <v>0.22</v>
+      </c>
+    </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="32">
+      <c r="A13" s="36">
         <v>1</v>
       </c>
-      <c r="B13" s="31" t="s">
-        <v>304</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>307</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>306</v>
-      </c>
-      <c r="E13" s="31" t="s">
-        <v>308</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="G13" s="31" t="s">
+      <c r="B13" s="37" t="s">
+        <v>298</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="D13" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>302</v>
+      </c>
+      <c r="F13" s="37" t="s">
+        <v>299</v>
+      </c>
+      <c r="G13" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="H13" s="31" t="s">
-        <v>309</v>
-      </c>
-      <c r="J13" s="37">
+      <c r="H13" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="J13" s="38">
         <v>0.46</v>
       </c>
-      <c r="K13" s="37">
+      <c r="K13" s="38">
         <f>J13*A13</f>
         <v>0.46</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="32">
+      <c r="A15" s="36">
         <v>1</v>
       </c>
-      <c r="B15" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>358</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="F15" s="31" t="s">
-        <v>357</v>
-      </c>
-      <c r="G15" s="31" t="s">
+      <c r="B15" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>217</v>
+      </c>
+      <c r="D15" s="39" t="s">
+        <v>347</v>
+      </c>
+      <c r="E15" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="F15" s="37" t="s">
+        <v>346</v>
+      </c>
+      <c r="G15" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="H15" s="31" t="s">
-        <v>356</v>
-      </c>
-      <c r="J15" s="37">
+      <c r="H15" s="37" t="s">
+        <v>345</v>
+      </c>
+      <c r="J15" s="38">
         <v>1.24</v>
       </c>
-      <c r="K15" s="37">
+      <c r="K15" s="38">
         <f>J15*A15</f>
         <v>1.24</v>
       </c>
-      <c r="L15" s="30" t="s">
+      <c r="L15" s="39" t="s">
+        <v>216</v>
+      </c>
+      <c r="M15" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="N15" s="39" t="s">
         <v>220</v>
       </c>
-      <c r="M15" s="30" t="s">
+      <c r="O15" s="39" t="s">
         <v>223</v>
       </c>
-      <c r="N15" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="O15" s="30" t="s">
-        <v>227</v>
-      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="32">
+      <c r="A16" s="36">
         <v>0</v>
       </c>
-      <c r="C16" s="31" t="s">
-        <v>315</v>
-      </c>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="37" t="s">
+        <v>309</v>
+      </c>
+      <c r="D16" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="37" t="s">
         <v>206</v>
       </c>
-      <c r="F16" s="31" t="s">
+      <c r="F16" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="H16" s="31" t="s">
+      <c r="H16" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="J16" s="37">
+      <c r="J16" s="38">
         <v>0.79</v>
       </c>
-      <c r="K16" s="37">
+      <c r="K16" s="38">
         <f>J16*A16</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="32">
+      <c r="A18" s="36">
         <v>1</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="39" t="s">
+        <v>224</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>225</v>
+      </c>
+      <c r="F18" s="39" t="s">
         <v>228</v>
       </c>
-      <c r="D18" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="F18" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="G18" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="H18" s="30">
+      <c r="G18" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="H18" s="39">
         <v>358</v>
       </c>
-      <c r="I18" s="31">
+      <c r="I18" s="37">
         <v>25</v>
       </c>
-      <c r="J18" s="37">
+      <c r="J18" s="38">
         <v>20</v>
       </c>
-      <c r="K18" s="37">
+      <c r="K18" s="38">
         <f>J18*A18</f>
         <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="32">
+      <c r="A19" s="36">
         <v>1</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="D19" s="37" t="s">
         <v>233</v>
       </c>
-      <c r="C19" s="30" t="s">
-        <v>236</v>
-      </c>
-      <c r="D19" s="31" t="s">
+      <c r="E19" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="F19" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="H19" s="39" t="s">
         <v>237</v>
       </c>
-      <c r="E19" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="F19" s="30" t="s">
-        <v>235</v>
-      </c>
-      <c r="G19" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="H19" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="I19" s="31">
+      <c r="I19" s="37">
         <v>0.05</v>
       </c>
-      <c r="J19" s="37">
+      <c r="J19" s="38">
         <v>0.65</v>
       </c>
-      <c r="K19" s="37">
+      <c r="K19" s="38">
         <f t="shared" ref="K19:K21" si="1">J19*A19</f>
         <v>0.65</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="32">
+      <c r="A20" s="36">
         <v>1</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="31" t="s">
-        <v>238</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>239</v>
-      </c>
-      <c r="E20" s="30" t="s">
+      <c r="C20" s="37" t="s">
         <v>234</v>
       </c>
-      <c r="F20" s="31" t="s">
+      <c r="D20" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="E20" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="F20" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="G20" s="31" t="s">
+      <c r="G20" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="H20" s="31" t="s">
-        <v>240</v>
-      </c>
-      <c r="I20" s="31">
+      <c r="H20" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="I20" s="37">
         <v>8</v>
       </c>
-      <c r="J20" s="37">
+      <c r="J20" s="38">
         <v>2.7</v>
       </c>
-      <c r="K20" s="37">
+      <c r="K20" s="38">
         <f t="shared" si="1"/>
         <v>2.7</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="32">
+      <c r="A21" s="36">
         <v>1</v>
       </c>
-      <c r="B21" s="31" t="s">
-        <v>243</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="D21" s="34" t="s">
-        <v>244</v>
-      </c>
-      <c r="E21" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>245</v>
-      </c>
-      <c r="G21" s="31" t="s">
+      <c r="B21" s="37" t="s">
+        <v>239</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="E21" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="F21" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="G21" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="H21" s="31" t="s">
-        <v>242</v>
-      </c>
-      <c r="I21" s="31">
+      <c r="H21" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="I21" s="37">
         <v>400</v>
       </c>
-      <c r="J21" s="37">
+      <c r="J21" s="38">
         <v>1.82</v>
       </c>
-      <c r="K21" s="37">
+      <c r="K21" s="38">
         <f t="shared" si="1"/>
         <v>1.82</v>
       </c>
     </row>
+    <row r="22" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="36">
+        <v>1</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>368</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>370</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>372</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>373</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="I22" s="37">
+        <v>1.2</v>
+      </c>
+      <c r="J22" s="38">
+        <v>26.6</v>
+      </c>
+      <c r="K22" s="38">
+        <v>26.6</v>
+      </c>
+    </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="32">
+      <c r="A23" s="36">
         <v>2</v>
       </c>
-      <c r="B23" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="C23" s="30" t="s">
+      <c r="B23" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E23" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="F23" s="39" t="s">
+        <v>250</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="H23" s="39" t="s">
         <v>252</v>
       </c>
-      <c r="D23" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="E23" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="G23" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="H23" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="I23" s="31">
+      <c r="I23" s="37">
         <v>1</v>
       </c>
-      <c r="J23" s="37">
+      <c r="J23" s="38">
         <v>0.6</v>
       </c>
-      <c r="K23" s="37">
+      <c r="K23" s="38">
         <f>J23*A23</f>
         <v>1.2</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="32">
+      <c r="A24" s="36">
         <v>1</v>
       </c>
-      <c r="B24" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>249</v>
-      </c>
-      <c r="E24" s="31" t="s">
-        <v>250</v>
-      </c>
-      <c r="F24" s="31" t="s">
-        <v>251</v>
-      </c>
-      <c r="G24" s="31" t="s">
+      <c r="B24" s="37" t="s">
+        <v>244</v>
+      </c>
+      <c r="C24" s="37" t="s">
+        <v>245</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>246</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="G24" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="H24" s="30" t="s">
-        <v>257</v>
+      <c r="H24" s="39" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B25" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>372</v>
+      </c>
+      <c r="F25" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="G25" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="H25" s="37" t="s">
+        <v>379</v>
+      </c>
+      <c r="I25" s="37">
+        <v>2.72</v>
+      </c>
+      <c r="J25" s="38">
+        <v>5.14</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="32">
+      <c r="A26" s="36">
         <v>1</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="C26" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="C26" s="31" t="s">
-        <v>280</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>279</v>
-      </c>
-      <c r="E26" s="35" t="s">
-        <v>278</v>
-      </c>
-      <c r="F26" s="31" t="s">
-        <v>277</v>
-      </c>
-      <c r="G26" s="31" t="s">
+      <c r="D26" s="37" t="s">
+        <v>275</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="G26" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="H26" s="31" t="s">
-        <v>355</v>
-      </c>
-      <c r="I26" s="31">
+      <c r="H26" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="I26" s="37">
         <v>0.33</v>
       </c>
-      <c r="J26" s="37">
+      <c r="J26" s="38">
         <v>1.73</v>
       </c>
-      <c r="K26" s="37">
+      <c r="K26" s="38">
         <f>J26*A26</f>
         <v>1.73</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="32">
+      <c r="A28" s="36">
         <v>2</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="C28" s="37" t="s">
         <v>281</v>
       </c>
-      <c r="C28" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="D28" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="E28" s="36" t="s">
-        <v>321</v>
-      </c>
-      <c r="F28" s="36" t="s">
-        <v>322</v>
-      </c>
-      <c r="G28" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="H28" s="36" t="s">
-        <v>323</v>
-      </c>
-      <c r="J28" s="37">
+      <c r="D28" s="37" t="s">
+        <v>278</v>
+      </c>
+      <c r="E28" s="41" t="s">
+        <v>315</v>
+      </c>
+      <c r="F28" s="41" t="s">
+        <v>316</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="H28" s="41" t="s">
+        <v>317</v>
+      </c>
+      <c r="J28" s="38">
         <v>0.1</v>
       </c>
-      <c r="K28" s="37">
-        <f t="shared" ref="K28:K34" si="2">J28*A28</f>
+      <c r="K28" s="38">
+        <f t="shared" ref="K28:K33" si="2">J28*A28</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="32">
+      <c r="A29" s="36">
         <v>1</v>
       </c>
-      <c r="B29" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="C29" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="D29" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="E29" s="36" t="s">
-        <v>321</v>
-      </c>
-      <c r="F29" s="36" t="s">
-        <v>324</v>
-      </c>
-      <c r="G29" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="H29" s="36" t="s">
-        <v>325</v>
-      </c>
-      <c r="J29" s="37">
+      <c r="B29" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>280</v>
+      </c>
+      <c r="D29" s="37" t="s">
+        <v>278</v>
+      </c>
+      <c r="E29" s="41" t="s">
+        <v>315</v>
+      </c>
+      <c r="F29" s="41" t="s">
+        <v>318</v>
+      </c>
+      <c r="G29" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="H29" s="41" t="s">
+        <v>319</v>
+      </c>
+      <c r="J29" s="38">
         <v>0.1</v>
       </c>
-      <c r="K29" s="37">
+      <c r="K29" s="38">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="32">
+      <c r="A30" s="36">
         <v>2</v>
       </c>
-      <c r="B30" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="C30" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="D30" s="31" t="s">
+      <c r="B30" s="37" t="s">
+        <v>380</v>
+      </c>
+      <c r="C30" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="E30" s="36" t="s">
+      <c r="D30" s="37" t="s">
+        <v>278</v>
+      </c>
+      <c r="E30" s="41" t="s">
+        <v>315</v>
+      </c>
+      <c r="F30" s="41" t="s">
+        <v>320</v>
+      </c>
+      <c r="G30" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="H30" s="41" t="s">
         <v>321</v>
       </c>
-      <c r="F30" s="36" t="s">
-        <v>327</v>
-      </c>
-      <c r="G30" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="H30" s="36" t="s">
-        <v>328</v>
-      </c>
-      <c r="J30" s="37">
+      <c r="J30" s="38">
         <v>0.1</v>
       </c>
-      <c r="K30" s="37">
+      <c r="K30" s="38">
         <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="32">
-        <v>1</v>
-      </c>
-      <c r="B31" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="C31" s="31" t="s">
-        <v>326</v>
-      </c>
-      <c r="D31" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>321</v>
-      </c>
-      <c r="F31" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="G31" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="H31" s="36" t="s">
-        <v>330</v>
-      </c>
-      <c r="J31" s="37">
+      <c r="A31" s="36">
+        <v>0</v>
+      </c>
+      <c r="B31" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="C31" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="D31" s="37" t="s">
+        <v>278</v>
+      </c>
+      <c r="E31" s="41" t="s">
+        <v>315</v>
+      </c>
+      <c r="F31" s="41" t="s">
+        <v>322</v>
+      </c>
+      <c r="G31" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="H31" s="41" t="s">
+        <v>323</v>
+      </c>
+      <c r="J31" s="38">
         <v>0.1</v>
       </c>
-      <c r="K31" s="37">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="32">
-        <v>0</v>
-      </c>
-      <c r="B32" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="C32" s="31" t="s">
-        <v>302</v>
-      </c>
-      <c r="D32" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="E32" s="36" t="s">
-        <v>321</v>
-      </c>
-      <c r="F32" s="36" t="s">
-        <v>331</v>
-      </c>
-      <c r="G32" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="H32" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="J32" s="37">
-        <v>0.1</v>
-      </c>
-      <c r="K32" s="37">
+      <c r="K31" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B32" s="42"/>
+    </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B33" s="33"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="32">
+      <c r="A33" s="36">
         <v>5</v>
       </c>
-      <c r="B34" s="31" t="s">
-        <v>289</v>
-      </c>
-      <c r="C34" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="E34" s="31" t="s">
-        <v>292</v>
-      </c>
-      <c r="F34" s="31" t="s">
-        <v>291</v>
-      </c>
-      <c r="G34" s="31" t="s">
+      <c r="B33" s="37" t="s">
+        <v>283</v>
+      </c>
+      <c r="C33" s="37" t="s">
+        <v>284</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>286</v>
+      </c>
+      <c r="F33" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="G33" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="H34" s="31" t="s">
-        <v>293</v>
-      </c>
-      <c r="J34" s="37">
+      <c r="H33" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="J33" s="38">
         <v>0.37</v>
       </c>
-      <c r="K34" s="37">
+      <c r="K33" s="38">
         <f t="shared" si="2"/>
         <v>1.85</v>
       </c>
     </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="36">
+        <v>1</v>
+      </c>
+      <c r="B34" s="37" t="s">
+        <v>290</v>
+      </c>
+      <c r="C34" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="D34" s="37" t="s">
+        <v>341</v>
+      </c>
+    </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="32">
+      <c r="A35" s="36">
         <v>1</v>
       </c>
-      <c r="B35" s="31" t="s">
-        <v>296</v>
-      </c>
-      <c r="C35" s="31" t="s">
+      <c r="B35" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="C35" s="37" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="36">
+        <v>1</v>
+      </c>
+      <c r="B36" s="37" t="s">
+        <v>292</v>
+      </c>
+      <c r="C36" s="37" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="36">
+        <v>1</v>
+      </c>
+      <c r="B37" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="C37" s="37" t="s">
         <v>295</v>
       </c>
-      <c r="D35" s="31" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="32">
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="36">
         <v>1</v>
       </c>
-      <c r="B36" s="31" t="s">
-        <v>294</v>
-      </c>
-      <c r="C36" s="31" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="32">
+      <c r="B38" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="C38" s="37" t="s">
+        <v>306</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>308</v>
+      </c>
+      <c r="F38" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="G38" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="H38" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="J38" s="38">
+        <v>0.79</v>
+      </c>
+      <c r="K38" s="38">
+        <f t="shared" ref="K38" si="3">J38*A38</f>
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="36">
         <v>1</v>
       </c>
-      <c r="B37" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="C37" s="31" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="32">
+      <c r="B39" s="37" t="s">
+        <v>381</v>
+      </c>
+      <c r="C39" s="37" t="s">
+        <v>382</v>
+      </c>
+      <c r="D39" s="37" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="36">
         <v>1</v>
       </c>
-      <c r="B38" s="31" t="s">
-        <v>300</v>
-      </c>
-      <c r="C38" s="31" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="32">
+      <c r="B40" s="37" t="s">
+        <v>310</v>
+      </c>
+      <c r="C40" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="G40" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>311</v>
+      </c>
+      <c r="J40" s="38">
+        <v>12.5</v>
+      </c>
+      <c r="K40" s="38">
+        <f t="shared" ref="K40" si="4">J40*A40</f>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A41" s="36">
         <v>1</v>
       </c>
-      <c r="B39" s="31" t="s">
-        <v>310</v>
-      </c>
-      <c r="C39" s="31" t="s">
-        <v>312</v>
-      </c>
-      <c r="E39" s="31" t="s">
-        <v>314</v>
-      </c>
-      <c r="F39" s="31" t="s">
-        <v>311</v>
-      </c>
-      <c r="G39" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="H39" s="31" t="s">
-        <v>313</v>
-      </c>
-      <c r="J39" s="37">
-        <v>0.79</v>
-      </c>
-      <c r="K39" s="37">
-        <f t="shared" ref="K39" si="3">J39*A39</f>
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="32">
+      <c r="B41" s="37" t="s">
+        <v>384</v>
+      </c>
+      <c r="C41" s="37" t="s">
+        <v>385</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="36">
         <v>1</v>
       </c>
-      <c r="B41" s="31" t="s">
-        <v>316</v>
-      </c>
-      <c r="C41" s="31" t="s">
-        <v>320</v>
-      </c>
-      <c r="E41" s="31" t="s">
-        <v>318</v>
-      </c>
-      <c r="F41" s="31" t="s">
-        <v>319</v>
-      </c>
-      <c r="G41" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="H41" s="31" t="s">
-        <v>317</v>
-      </c>
-      <c r="J41" s="37">
-        <v>12.5</v>
-      </c>
-      <c r="K41" s="37">
-        <f t="shared" ref="K41" si="4">J41*A41</f>
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="32">
-        <v>1</v>
-      </c>
-      <c r="B43" s="31" t="s">
-        <v>349</v>
-      </c>
-      <c r="C43" s="31" t="s">
-        <v>350</v>
-      </c>
-      <c r="D43" s="31" t="s">
-        <v>352</v>
-      </c>
-      <c r="E43" s="31" t="s">
-        <v>351</v>
-      </c>
-      <c r="G43" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="J43" s="37">
+      <c r="B42" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="C42" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="D42" s="37" t="s">
+        <v>341</v>
+      </c>
+      <c r="E42" s="37" t="s">
+        <v>340</v>
+      </c>
+      <c r="G42" s="37" t="s">
+        <v>342</v>
+      </c>
+      <c r="J42" s="38">
         <v>4.75</v>
       </c>
-      <c r="K43" s="37">
-        <f t="shared" ref="K43" si="5">J43*A43</f>
+      <c r="K42" s="38">
+        <f t="shared" ref="K42" si="5">J42*A42</f>
         <v>4.75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="36">
+        <v>4</v>
+      </c>
+      <c r="B43" s="37" t="s">
+        <v>387</v>
+      </c>
+      <c r="C43" s="37" t="s">
+        <v>388</v>
+      </c>
+      <c r="D43" s="37" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -16925,10 +17156,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="D1" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -16939,7 +17170,7 @@
         <v>177</v>
       </c>
       <c r="C2" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -16950,10 +17181,10 @@
         <v>178</v>
       </c>
       <c r="C3" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="D3" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -16964,10 +17195,10 @@
         <v>178</v>
       </c>
       <c r="C4" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="D4" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -16978,10 +17209,10 @@
         <v>178</v>
       </c>
       <c r="C5" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="D5" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -16992,10 +17223,10 @@
         <v>179</v>
       </c>
       <c r="C6" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="D6" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -17006,10 +17237,10 @@
         <v>178</v>
       </c>
       <c r="C7" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="D7" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -17020,10 +17251,10 @@
         <v>178</v>
       </c>
       <c r="C8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="D8" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -17034,10 +17265,10 @@
         <v>178</v>
       </c>
       <c r="C9" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="D9" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
